--- a/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>ISPO</t>
   </si>
@@ -656,114 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E8" s="3">
         <v>82600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>84100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>91700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>86600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>93100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>83700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>82100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -776,8 +779,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -785,35 +788,38 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E9" s="3">
         <v>57700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>64700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>60100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>60700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>63000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>57400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,35 +841,38 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E10" s="3">
         <v>24900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>31600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,35 +917,36 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E12" s="3">
         <v>2400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2800</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -955,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,40 +1021,43 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E14" s="3">
         <v>4300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>30100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1055,13 +1074,16 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>1000</v>
@@ -1073,16 +1095,16 @@
         <v>1000</v>
       </c>
       <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
         <v>800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>700</v>
       </c>
       <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>700</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
@@ -1096,8 +1118,8 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1105,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,85 +1147,89 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E17" s="3">
         <v>107500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>130500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>97400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>101000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>88500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>106100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
-      </c>
-      <c r="O17" s="3">
-        <v>100</v>
       </c>
       <c r="P17" s="3">
         <v>100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+      <c r="Q17" s="3">
+        <v>100</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-46400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-24000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,17 +1242,20 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1274,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1268,8 +1301,8 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1283,44 +1316,47 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-44600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-23000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,66 +1431,72 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-46500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>200</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
@@ -1468,8 +1513,8 @@
       <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>200</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1483,8 +1528,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1492,8 +1537,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-46700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,8 +1908,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1868,8 +1937,8 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1883,67 +1952,73 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2222,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E41" s="3">
         <v>49700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>44400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>59900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>121300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>133100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,35 +2326,38 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E43" s="3">
         <v>2100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,8 +2370,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2287,8 +2379,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2337,134 +2432,143 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E45" s="3">
         <v>28100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>36900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>36800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>500</v>
       </c>
       <c r="O45" s="3">
         <v>500</v>
       </c>
       <c r="P45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E46" s="3">
         <v>79900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>104700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>116900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>115100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>161600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>169000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
-        <v>176000</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>176000</v>
@@ -2478,8 +2582,8 @@
       <c r="O47" s="3">
         <v>176000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>176000</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2487,35 +2591,38 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>229200</v>
+      </c>
+      <c r="E48" s="3">
         <v>246600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>253400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>276300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>290000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>270200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>248300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>199300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,8 +2635,8 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -2537,8 +2644,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2563,8 +2673,8 @@
       <c r="J49" s="3">
         <v>21200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>21200</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2578,8 +2688,8 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2587,8 +2697,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,35 +2803,38 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E52" s="3">
         <v>5600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2728,8 +2847,8 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -2737,8 +2856,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2909,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>330700</v>
+      </c>
+      <c r="E54" s="3">
         <v>353300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>365400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>406300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>430400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>407700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>432200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>390600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>176300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>176600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>176900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>177300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>177700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,58 +3006,62 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E57" s="3">
         <v>14500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>31500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2941,21 +3074,21 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>14000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2968,8 +3101,8 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -2977,37 +3110,40 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>233600</v>
+      </c>
+      <c r="E59" s="3">
         <v>229200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>227600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>231900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>247500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>235100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>246200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>240100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
-      </c>
-      <c r="L59" s="3">
-        <v>200</v>
       </c>
       <c r="M59" s="3">
         <v>200</v>
@@ -3019,75 +3155,81 @@
         <v>200</v>
       </c>
       <c r="P59" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>245200</v>
+      </c>
+      <c r="E60" s="3">
         <v>243700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>258900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>263900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>278100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>266100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>295500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>284800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E61" s="3">
         <v>25000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -3119,66 +3261,72 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>216400</v>
+      </c>
+      <c r="E62" s="3">
         <v>226200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>229500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>222400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>227200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>205300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>199000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>168200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3481,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>377400</v>
+        <v>361000</v>
       </c>
       <c r="E66" s="3">
         <v>377400</v>
       </c>
       <c r="F66" s="3">
+        <v>377400</v>
+      </c>
+      <c r="G66" s="3">
         <v>397900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>418600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>390300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>413800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>376600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3767,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-285800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-277000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-260300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-236900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-233900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-231300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-226400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-223400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-21500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3979,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-24100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-12000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>149600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>150800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>148900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>160600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>154500</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,35 +4219,36 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3">
         <v>3300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1900</v>
       </c>
       <c r="G83" s="3">
         <v>1900</v>
       </c>
       <c r="H83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4063,8 +4261,8 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4072,8 +4270,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,40 +4611,41 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4433,8 +4653,8 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4442,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,35 +4768,38 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4583,8 +4812,8 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -4592,8 +4821,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4636,11 +4869,11 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-200</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4662,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,35 +5054,38 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>25100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-12700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>66000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4853,8 +5098,8 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -4862,8 +5107,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5160,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-39300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>52100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>ISPO</t>
   </si>
@@ -656,120 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E8" s="3">
         <v>70700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>82600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>84100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>91700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>86600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>93100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>83700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>82100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -782,8 +786,8 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -791,38 +795,41 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E9" s="3">
         <v>51500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>57700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>64700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>60100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>60700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>63000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>57400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,38 +851,41 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E10" s="3">
         <v>19200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>30100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>26300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,38 +931,39 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E12" s="3">
         <v>2600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2800</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +985,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,43 +1041,46 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>6500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>30100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1077,16 +1097,19 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1000</v>
       </c>
       <c r="F15" s="3">
         <v>1000</v>
@@ -1098,16 +1121,16 @@
         <v>1000</v>
       </c>
       <c r="I15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>700</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1121,8 +1144,8 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,91 +1174,95 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E17" s="3">
         <v>86800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>107500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>130500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>97400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>101000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>88500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>106100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
-      </c>
-      <c r="P17" s="3">
-        <v>100</v>
       </c>
       <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>100</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-46400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1245,17 +1275,20 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1308,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1304,8 +1338,8 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1319,47 +1353,50 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-44600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-12500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-23000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1418,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1434,72 +1474,78 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-46500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
@@ -1516,8 +1562,8 @@
       <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>200</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1531,8 +1577,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-46700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +1978,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1940,8 +2010,8 @@
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1955,70 +2025,76 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,61 +2309,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E41" s="3">
         <v>36600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>44400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>80300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>121300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,38 +2419,41 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,8 +2466,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2382,8 +2475,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,114 +2531,123 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E45" s="3">
         <v>34100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>500</v>
       </c>
       <c r="P45" s="3">
         <v>500</v>
       </c>
       <c r="Q45" s="3">
+        <v>500</v>
+      </c>
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E46" s="3">
         <v>74800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>79900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>85000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>104700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>116900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>115100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>161600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>169000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2567,11 +2672,11 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
-        <v>176000</v>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>176000</v>
@@ -2585,8 +2690,8 @@
       <c r="P47" s="3">
         <v>176000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>176000</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2594,38 +2699,41 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>225300</v>
+      </c>
+      <c r="E48" s="3">
         <v>229200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>246600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>253400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>276300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>290000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>270200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>248300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>199300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2638,8 +2746,8 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2647,8 +2755,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2676,8 +2787,8 @@
       <c r="K49" s="3">
         <v>21200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>21200</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2691,8 +2802,8 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,38 +2923,41 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2850,8 +2970,8 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,61 +3035,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E54" s="3">
         <v>330700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>353300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>365400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>406300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>430400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>407700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>432200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>390600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>176300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>176600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>176900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>177300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>177700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,61 +3137,65 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E57" s="3">
         <v>11600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3077,21 +3211,21 @@
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>14000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3238,8 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3113,40 +3247,43 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>215400</v>
+      </c>
+      <c r="E59" s="3">
         <v>233600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>229200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>227600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>231900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>247500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>235100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>246200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>240100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
-      </c>
-      <c r="M59" s="3">
-        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
@@ -3158,81 +3295,87 @@
         <v>200</v>
       </c>
       <c r="Q59" s="3">
+        <v>200</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E60" s="3">
         <v>245200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>243700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>258900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>263900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>278100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>266100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>295500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>284800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E61" s="3">
         <v>23900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -3264,69 +3407,75 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>215100</v>
+      </c>
+      <c r="E62" s="3">
         <v>216400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>226200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>229500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>222400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>227200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>205300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>199000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>168200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,61 +3639,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>340500</v>
+      </c>
+      <c r="E66" s="3">
         <v>361000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>377400</v>
       </c>
       <c r="F66" s="3">
         <v>377400</v>
       </c>
       <c r="G66" s="3">
+        <v>377400</v>
+      </c>
+      <c r="H66" s="3">
         <v>397900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>418600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>390300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>413800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>376600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>300</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,61 +3941,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-284500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-285800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-277000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-260300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-236900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-233900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-231300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-226400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-223400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,61 +4165,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-30200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-24100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-12000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>149600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>150800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>148900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>160600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>154500</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,38 +4418,39 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E83" s="3">
         <v>3500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1900</v>
       </c>
       <c r="H83" s="3">
         <v>1900</v>
       </c>
       <c r="I83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,8 +4463,8 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -4273,8 +4472,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4752,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,43 +4832,44 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -4656,8 +4877,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -4665,8 +4886,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,38 +4998,41 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4815,8 +5045,8 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -4824,8 +5054,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5078,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4872,11 +5106,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,38 +5300,41 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>25100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-12700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>66000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5101,8 +5347,8 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -5110,8 +5356,11 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5163,57 +5412,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-39300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>52100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>ISPO</t>
   </si>
@@ -656,127 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E8" s="3">
         <v>80200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>70700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>82600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>84100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>91700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>86600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>93100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>83700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>82100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -789,8 +793,8 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -798,41 +802,44 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E9" s="3">
         <v>48500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>51500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>57700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>64700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>60100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>60700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>63000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>57400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -854,41 +861,44 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E10" s="3">
         <v>31700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>26300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,41 +945,42 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E12" s="3">
         <v>2100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2400</v>
       </c>
-      <c r="G12" s="3">
-        <v>3000</v>
-      </c>
       <c r="H12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I12" s="3">
         <v>3400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2800</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,46 +1061,49 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>6500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>30100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1100,19 +1120,22 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1000</v>
       </c>
       <c r="G15" s="3">
         <v>1000</v>
@@ -1124,16 +1147,16 @@
         <v>1000</v>
       </c>
       <c r="J15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="3">
         <v>800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>700</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1147,8 +1170,8 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1156,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,97 +1201,101 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E17" s="3">
         <v>77900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>86800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>107500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>130500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>97400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>101000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>100200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>88500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>106100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>100</v>
       </c>
       <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>100</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-46400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,17 +1308,20 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,8 +1342,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1341,8 +1375,8 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1356,50 +1390,53 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E21" s="3">
         <v>5000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-12500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-21600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-44600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-23000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,8 +1458,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1477,64 +1517,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-46500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1542,13 +1588,13 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>200</v>
       </c>
       <c r="H24" s="3">
         <v>200</v>
@@ -1565,8 +1611,8 @@
       <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>200</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1580,8 +1626,8 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1589,8 +1635,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-46700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,8 +2048,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2013,8 +2083,8 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -2028,73 +2098,79 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,64 +2396,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E41" s="3">
         <v>22600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>44400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>80300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>121300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2422,41 +2512,44 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2562,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2478,8 +2571,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2534,120 +2630,129 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E45" s="3">
         <v>35600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>500</v>
       </c>
       <c r="Q45" s="3">
         <v>500</v>
       </c>
       <c r="R45" s="3">
+        <v>500</v>
+      </c>
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E46" s="3">
         <v>61500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>79900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>85000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>104700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>116900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>115100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>161600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>169000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2675,11 +2780,11 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
-        <v>176000</v>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>176000</v>
@@ -2693,8 +2798,8 @@
       <c r="Q47" s="3">
         <v>176000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>176000</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2702,41 +2807,44 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>216600</v>
+      </c>
+      <c r="E48" s="3">
         <v>225300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>229200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>246600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>253400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>276300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>290000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>270200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>248300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>199300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,8 +2857,8 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -2758,8 +2866,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2790,8 +2901,8 @@
       <c r="L49" s="3">
         <v>21200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>21200</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2805,8 +2916,8 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2814,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,41 +3043,44 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
         <v>5000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2973,8 +3093,8 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -2982,8 +3102,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>301700</v>
+      </c>
+      <c r="E54" s="3">
         <v>313000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>330700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>353300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>365400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>406300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>430400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>407700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>432200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>390600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>176300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>176600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>176900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>177300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>177700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,81 +3268,85 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E57" s="3">
         <v>12200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>31000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -3221,14 +3355,14 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>14000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3241,8 +3375,8 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3250,43 +3384,46 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>219900</v>
+      </c>
+      <c r="E59" s="3">
         <v>215400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>233600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>229200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>227600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>231900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>247500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>235100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>246200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>240100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>200</v>
@@ -3298,87 +3435,93 @@
         <v>200</v>
       </c>
       <c r="R59" s="3">
+        <v>200</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E60" s="3">
         <v>227600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>245200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>243700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>258900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>263900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>278100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>266100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>295500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>284800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E61" s="3">
         <v>20200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -3410,72 +3553,78 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>212600</v>
+      </c>
+      <c r="E62" s="3">
         <v>215100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>216400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>226200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>229500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>222400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>227200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>205300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>199000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>168200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>336900</v>
+      </c>
+      <c r="E66" s="3">
         <v>340500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>361000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>377400</v>
       </c>
       <c r="G66" s="3">
         <v>377400</v>
       </c>
       <c r="H66" s="3">
+        <v>377400</v>
+      </c>
+      <c r="I66" s="3">
         <v>397900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>418600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>390300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>413800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>376600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-293200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-284500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-285800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-277000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-260300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-236900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-233900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-231300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-226400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-223400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-21500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-27500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-30200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-24100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-12000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>149600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>150800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>148900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>160600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>154500</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,41 +4617,42 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E83" s="3">
         <v>2600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1900</v>
       </c>
       <c r="I83" s="3">
         <v>1900</v>
       </c>
       <c r="J83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4466,8 +4665,8 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4475,8 +4674,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,46 +5053,47 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4880,8 +5101,8 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -4889,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,41 +5228,44 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5048,8 +5278,8 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -5057,8 +5287,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5109,11 +5343,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5135,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,41 +5546,44 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>25100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-12700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>66000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5350,8 +5596,8 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -5359,8 +5605,11 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5415,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-39300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>52100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>ISPO</t>
   </si>
@@ -656,134 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E8" s="3">
         <v>67400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>80200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>70700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>82600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>84100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>91700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>86600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>93100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>83700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>82100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -796,8 +800,8 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -805,44 +809,47 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E9" s="3">
         <v>51200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>48500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>51500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>57700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>64700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>60100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>60700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>63000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>57400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>47300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,44 +871,47 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E10" s="3">
         <v>16200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,44 +959,45 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="3">
         <v>2300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2600</v>
       </c>
-      <c r="G12" s="3">
-        <v>2400</v>
-      </c>
       <c r="H12" s="3">
-        <v>6300</v>
+        <v>2700</v>
       </c>
       <c r="I12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J12" s="3">
         <v>3400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2800</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,49 +1081,52 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-21100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>6500</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H14" s="3">
         <v>4300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>30100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1123,22 +1143,25 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="3">
         <v>800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1000</v>
       </c>
       <c r="H15" s="3">
         <v>1000</v>
@@ -1150,16 +1173,16 @@
         <v>1000</v>
       </c>
       <c r="K15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="3">
         <v>800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>700</v>
       </c>
       <c r="M15" s="3">
         <v>700</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>700</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
@@ -1173,8 +1196,8 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,103 +1228,107 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>82700</v>
+        <v>82800</v>
       </c>
       <c r="E17" s="3">
-        <v>77900</v>
+        <v>82000</v>
       </c>
       <c r="F17" s="3">
-        <v>86800</v>
+        <v>82000</v>
       </c>
       <c r="G17" s="3">
-        <v>107500</v>
+        <v>82100</v>
       </c>
       <c r="H17" s="3">
-        <v>130500</v>
+        <v>101800</v>
       </c>
       <c r="I17" s="3">
+        <v>101000</v>
+      </c>
+      <c r="J17" s="3">
         <v>97400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>101000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>100200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>88500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>106100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
-      </c>
-      <c r="R17" s="3">
-        <v>100</v>
       </c>
       <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>100</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-15300</v>
+        <v>-13700</v>
       </c>
       <c r="E18" s="3">
-        <v>2300</v>
+        <v>-14600</v>
       </c>
       <c r="F18" s="3">
-        <v>-16100</v>
+        <v>-1700</v>
       </c>
       <c r="G18" s="3">
-        <v>-24900</v>
+        <v>-11400</v>
       </c>
       <c r="H18" s="3">
-        <v>-46400</v>
+        <v>-19200</v>
       </c>
       <c r="I18" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,17 +1341,20 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,31 +1376,32 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-4400</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1378,8 +1412,8 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1393,53 +1427,56 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-12500</v>
       </c>
-      <c r="E21" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-21600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-44600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-23000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1461,31 +1498,34 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1520,84 +1560,90 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-46500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>200</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
@@ -1614,8 +1660,8 @@
       <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>200</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1629,8 +1675,8 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-46700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,31 +2118,34 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2086,8 +2156,8 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -2101,76 +2171,82 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E41" s="3">
         <v>18800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>44400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>80300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>121300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>133100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,44 +2605,47 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E43" s="3">
         <v>4200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4100</v>
       </c>
-      <c r="G43" s="3">
-        <v>2100</v>
-      </c>
       <c r="H43" s="3">
-        <v>3700</v>
+        <v>2900</v>
       </c>
       <c r="I43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J43" s="3">
         <v>6400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2565,8 +2658,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2574,31 +2667,34 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2633,149 +2729,158 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>36000</v>
+        <v>1900</v>
       </c>
       <c r="E45" s="3">
-        <v>35600</v>
+        <v>1900</v>
       </c>
       <c r="F45" s="3">
-        <v>34100</v>
+        <v>1800</v>
       </c>
       <c r="G45" s="3">
-        <v>28100</v>
+        <v>1700</v>
       </c>
       <c r="H45" s="3">
-        <v>36900</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="3">
-        <v>38400</v>
+        <v>400</v>
       </c>
       <c r="J45" s="3">
+        <v>600</v>
+      </c>
+      <c r="K45" s="3">
         <v>32800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>500</v>
       </c>
       <c r="R45" s="3">
         <v>500</v>
       </c>
       <c r="S45" s="3">
+        <v>500</v>
+      </c>
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E46" s="3">
         <v>59000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>74800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>79900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>85000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>104700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>116900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>115100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>161600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>169000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2783,11 +2888,11 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
-        <v>176000</v>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>176000</v>
@@ -2801,8 +2906,8 @@
       <c r="R47" s="3">
         <v>176000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>176000</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2810,44 +2915,47 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>199300</v>
+      </c>
+      <c r="E48" s="3">
         <v>216600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>225300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>229200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>246600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>253400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>276300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>290000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>270200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>248300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>199300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2968,8 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2869,8 +2977,11 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2904,8 +3015,8 @@
       <c r="M49" s="3">
         <v>21200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>21200</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2919,8 +3030,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,44 +3163,47 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H52" s="3">
         <v>4800</v>
       </c>
-      <c r="E52" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>5600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>5800</v>
-      </c>
       <c r="I52" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J52" s="3">
         <v>4000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,8 +3216,8 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>273300</v>
+      </c>
+      <c r="E54" s="3">
         <v>301700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>313000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>330700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>353300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>365400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>406300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>430400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>407700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>432200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>390600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>176300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>176600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>176900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>177300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>177700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,103 +3399,107 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E57" s="3">
         <v>10700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>55300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>61300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>62900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>64900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>65900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>67100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>14000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3512,8 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3387,46 +3521,49 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>219900</v>
+        <v>136100</v>
       </c>
       <c r="E59" s="3">
-        <v>215400</v>
+        <v>149000</v>
       </c>
       <c r="F59" s="3">
-        <v>233600</v>
+        <v>143000</v>
       </c>
       <c r="G59" s="3">
-        <v>229200</v>
+        <v>161000</v>
       </c>
       <c r="H59" s="3">
-        <v>227600</v>
+        <v>153600</v>
       </c>
       <c r="I59" s="3">
-        <v>231900</v>
+        <v>160000</v>
       </c>
       <c r="J59" s="3">
+        <v>163300</v>
+      </c>
+      <c r="K59" s="3">
         <v>247500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>235100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>246200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>240100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
-      </c>
-      <c r="O59" s="3">
-        <v>200</v>
       </c>
       <c r="P59" s="3">
         <v>200</v>
@@ -3438,98 +3575,104 @@
         <v>200</v>
       </c>
       <c r="S59" s="3">
+        <v>200</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E60" s="3">
         <v>230600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>227600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>245200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>243700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>258900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>263900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>278100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>266100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>295500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>284800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>21000</v>
+        <v>159000</v>
       </c>
       <c r="E61" s="3">
-        <v>20200</v>
+        <v>206200</v>
       </c>
       <c r="F61" s="3">
-        <v>23900</v>
+        <v>212400</v>
       </c>
       <c r="G61" s="3">
-        <v>25000</v>
+        <v>220700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>229100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>209900</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>202600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3556,75 +3699,81 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>212600</v>
+        <v>3200</v>
       </c>
       <c r="E62" s="3">
-        <v>215100</v>
+        <v>3000</v>
       </c>
       <c r="F62" s="3">
-        <v>216400</v>
+        <v>2900</v>
       </c>
       <c r="G62" s="3">
-        <v>226200</v>
+        <v>2500</v>
       </c>
       <c r="H62" s="3">
-        <v>229500</v>
+        <v>2900</v>
       </c>
       <c r="I62" s="3">
-        <v>222400</v>
+        <v>500</v>
       </c>
       <c r="J62" s="3">
+        <v>900</v>
+      </c>
+      <c r="K62" s="3">
         <v>227200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>205300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>199000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>168200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>22800</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>336900</v>
+        <v>407900</v>
       </c>
       <c r="E66" s="3">
-        <v>340500</v>
+        <v>464200</v>
       </c>
       <c r="F66" s="3">
-        <v>361000</v>
+        <v>462900</v>
       </c>
       <c r="G66" s="3">
-        <v>377400</v>
+        <v>485400</v>
       </c>
       <c r="H66" s="3">
-        <v>377400</v>
+        <v>494900</v>
       </c>
       <c r="I66" s="3">
-        <v>397900</v>
+        <v>488300</v>
       </c>
       <c r="J66" s="3">
+        <v>486300</v>
+      </c>
+      <c r="K66" s="3">
         <v>418600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>390300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>413800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>376600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-288900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-293200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-284500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-285800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-277000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-260300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-236900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-233900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-231300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-226400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-223400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-21500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-134600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-35200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-27500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-30200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-24100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-12000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>149600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>150800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>148900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>160600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>154500</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,44 +4816,45 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2800</v>
+        <v>24400</v>
       </c>
       <c r="E83" s="3">
-        <v>2600</v>
+        <v>18700</v>
       </c>
       <c r="F83" s="3">
-        <v>3500</v>
+        <v>27400</v>
       </c>
       <c r="G83" s="3">
-        <v>3300</v>
+        <v>21500</v>
       </c>
       <c r="H83" s="3">
-        <v>1800</v>
+        <v>24000</v>
       </c>
       <c r="I83" s="3">
+        <v>33800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>14300</v>
+      </c>
+      <c r="K83" s="3">
         <v>1900</v>
       </c>
-      <c r="J83" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4668,8 +4867,8 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,49 +5274,50 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2000</v>
+        <v>-1100</v>
       </c>
       <c r="E91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3700</v>
-      </c>
       <c r="H91" s="3">
-        <v>-3800</v>
+        <v>-2300</v>
       </c>
       <c r="I91" s="3">
-        <v>-3200</v>
+        <v>-1200</v>
       </c>
       <c r="J91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5104,8 +5325,8 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,44 +5458,47 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5281,8 +5511,8 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,31 +5546,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5346,11 +5580,11 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,44 +5792,47 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>25100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-12700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>66000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5599,8 +5845,8 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -5608,31 +5854,34 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>52100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1200</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>ISPO</t>
   </si>
@@ -656,141 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E8" s="3">
         <v>69100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>80200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>70700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>82600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>84100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>91700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>86600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>93100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>83700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>82100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,8 +806,8 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -812,47 +815,50 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E9" s="3">
         <v>49600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>51200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>48500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>51500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>57700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>64700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>60100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>60700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>63000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>57400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -874,47 +880,50 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E10" s="3">
         <v>19500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>31700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,47 +972,48 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2800</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,52 +1100,55 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-21100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>6100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>30100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1146,8 +1165,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1161,10 +1183,10 @@
         <v>1000</v>
       </c>
       <c r="G15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="3">
         <v>800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1000</v>
       </c>
       <c r="I15" s="3">
         <v>1000</v>
@@ -1176,16 +1198,16 @@
         <v>1000</v>
       </c>
       <c r="L15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M15" s="3">
         <v>800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>700</v>
       </c>
       <c r="N15" s="3">
         <v>700</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>700</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1199,8 +1221,8 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1208,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,109 +1254,113 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E17" s="3">
         <v>82800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>82000</v>
       </c>
       <c r="F17" s="3">
         <v>82000</v>
       </c>
       <c r="G17" s="3">
+        <v>82000</v>
+      </c>
+      <c r="H17" s="3">
         <v>82100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>101800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>101000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>97400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>101000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>88500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>106100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
-      </c>
-      <c r="S17" s="3">
-        <v>100</v>
       </c>
       <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>100</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1344,17 +1373,20 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,35 +1409,36 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1415,8 +1448,8 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1430,56 +1463,59 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-23000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1501,34 +1537,37 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1563,70 +1602,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-46500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1634,19 +1679,19 @@
         <v>200</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
@@ -1663,8 +1708,8 @@
       <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>200</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1678,8 +1723,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1687,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-46700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-11700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,35 +2187,38 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2159,8 +2228,8 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -2174,79 +2243,85 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2569,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E41" s="3">
         <v>13500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>44400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>80300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>82100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>121300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,47 +2697,50 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E43" s="3">
         <v>3400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2661,8 +2753,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2670,8 +2762,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2696,8 +2791,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2732,8 +2827,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2744,120 +2842,126 @@
         <v>1900</v>
       </c>
       <c r="F45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
-      </c>
-      <c r="R45" s="3">
-        <v>500</v>
       </c>
       <c r="S45" s="3">
         <v>500</v>
       </c>
       <c r="T45" s="3">
+        <v>500</v>
+      </c>
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E46" s="3">
         <v>47900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>61500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>74800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>79900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>85000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>104700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>116900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>115100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>161600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>169000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2882,8 +2986,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2891,11 +2995,11 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>176000</v>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>176000</v>
@@ -2909,8 +3013,8 @@
       <c r="S47" s="3">
         <v>176000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>176000</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -2918,47 +3022,50 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>189300</v>
+      </c>
+      <c r="E48" s="3">
         <v>199300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>216600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>225300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>229200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>246600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>253400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>276300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>290000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>270200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>248300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>199300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2971,8 +3078,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2980,8 +3087,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3018,8 +3128,8 @@
       <c r="N49" s="3">
         <v>21200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>21200</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -3033,8 +3143,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3042,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,47 +3282,50 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3338,8 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3228,8 +3347,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>273900</v>
+      </c>
+      <c r="E54" s="3">
         <v>273300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>301700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>313000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>330700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>353300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>365400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>406300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>430400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>407700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>432200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>390600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>176300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>176600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>176900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>177300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>177700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,109 +3529,113 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E58" s="3">
         <v>55300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>61300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>62900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>62000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>64900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>65900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>67100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>14000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3515,8 +3648,8 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3524,49 +3657,52 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>135300</v>
+      </c>
+      <c r="E59" s="3">
         <v>136100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>149000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>143000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>161000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>153600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>160000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>163300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>247500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>235100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>246200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>240100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>200</v>
@@ -3578,105 +3714,111 @@
         <v>200</v>
       </c>
       <c r="T59" s="3">
+        <v>200</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E60" s="3">
         <v>217500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>230600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>227600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>245200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>243700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>258900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>263900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>278100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>266100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>295500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>284800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>152600</v>
+      </c>
+      <c r="E61" s="3">
         <v>159000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>206200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>212400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>220700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>229100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>209900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>202600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3702,16 +3844,19 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3719,61 +3864,64 @@
         <v>3200</v>
       </c>
       <c r="E62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F62" s="3">
         <v>3000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>227200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>205300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>199000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>168200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>27500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22800</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>403700</v>
+      </c>
+      <c r="E66" s="3">
         <v>407900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>464200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>462900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>485400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>494900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>488300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>486300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>418600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>390300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>413800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>376600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>300</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4462,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-291200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-288900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-293200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-284500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-285800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-277000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-260300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-236900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-233900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-231300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-226400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-223400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-21500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4722,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-129900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-134600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-35200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-27500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-30200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-24100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-12000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>149600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>150800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>148900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>160600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>154500</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,47 +5014,48 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E83" s="3">
         <v>24400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>33800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4870,8 +5068,8 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4879,8 +5077,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,52 +5494,53 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3900</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5328,8 +5548,8 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5337,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,47 +5687,50 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5514,8 +5743,8 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5523,8 +5752,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5573,8 +5806,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5583,11 +5816,11 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -5609,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,47 +6037,50 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E100" s="3">
         <v>9700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>25100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-12700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>66000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5848,8 +6093,8 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -5857,8 +6102,11 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5883,8 +6131,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5919,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>52100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1200</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>ISPO</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E8" s="3">
         <v>63100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>69100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>67400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>80200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>70700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>82600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>84100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>86600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>93100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>83700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>82100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,8 +813,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -818,50 +822,53 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E9" s="3">
         <v>41200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>51200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>48500</v>
       </c>
-      <c r="H9" s="3">
-        <v>51500</v>
-      </c>
       <c r="I9" s="3">
+        <v>51400</v>
+      </c>
+      <c r="J9" s="3">
         <v>57700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>64700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>60100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>60700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>63000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>57400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -883,50 +890,53 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E10" s="3">
         <v>21900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31700</v>
       </c>
-      <c r="H10" s="3">
-        <v>19200</v>
-      </c>
       <c r="I10" s="3">
+        <v>19300</v>
+      </c>
+      <c r="J10" s="3">
         <v>24900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>34800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -948,8 +958,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,50 +986,51 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
         <v>1400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2100</v>
       </c>
-      <c r="H12" s="3">
-        <v>2600</v>
-      </c>
       <c r="I12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J12" s="3">
         <v>2700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2800</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1052,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,55 +1120,58 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-600</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F14" s="3">
         <v>-21100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>6100</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J14" s="3">
         <v>4300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>30100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1168,8 +1188,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1186,10 +1209,10 @@
         <v>1000</v>
       </c>
       <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
         <v>800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1000</v>
       </c>
       <c r="J15" s="3">
         <v>1000</v>
@@ -1201,16 +1224,16 @@
         <v>1000</v>
       </c>
       <c r="M15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N15" s="3">
         <v>800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>700</v>
       </c>
       <c r="O15" s="3">
         <v>700</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>700</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1224,8 +1247,8 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1233,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,115 +1281,119 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>65100</v>
+        <v>64300</v>
       </c>
       <c r="E17" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F17" s="3">
         <v>82800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>82000</v>
       </c>
       <c r="G17" s="3">
         <v>82000</v>
       </c>
       <c r="H17" s="3">
+        <v>82000</v>
+      </c>
+      <c r="I17" s="3">
         <v>82100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>101800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>101000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>97400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>101000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>88500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>106100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
-      </c>
-      <c r="T17" s="3">
-        <v>100</v>
       </c>
       <c r="U17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>100</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2000</v>
+        <v>1600</v>
       </c>
       <c r="E18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-13700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1376,17 +1406,20 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,38 +1443,39 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4400</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1400</v>
-      </c>
       <c r="I20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1451,8 +1485,8 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1466,59 +1500,62 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1100</v>
+        <v>3100</v>
       </c>
       <c r="E21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3700</v>
       </c>
-      <c r="H21" s="3">
-        <v>-9200</v>
-      </c>
       <c r="I21" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-17900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-23000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,37 +1577,40 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
         <v>600</v>
       </c>
       <c r="F22" s="3">
+        <v>600</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
-        <v>300</v>
-      </c>
       <c r="H22" s="3">
+        <v>500</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1605,96 +1645,102 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>200</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
@@ -1711,8 +1757,8 @@
       <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>200</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1726,8 +1772,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1735,8 +1781,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-46700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,38 +2257,41 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4400</v>
       </c>
-      <c r="H32" s="3">
-        <v>1400</v>
-      </c>
       <c r="I32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2231,8 +2301,8 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -2246,82 +2316,88 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,73 +2656,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E41" s="3">
         <v>21800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>44400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>80300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>121300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2700,50 +2790,53 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2700</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2756,8 +2849,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2765,8 +2858,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2794,8 +2890,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2830,13 +2926,16 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E45" s="3">
         <v>1900</v>
@@ -2845,123 +2944,129 @@
         <v>1900</v>
       </c>
       <c r="G45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
-      </c>
-      <c r="S45" s="3">
-        <v>500</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
       </c>
       <c r="U45" s="3">
+        <v>500</v>
+      </c>
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E46" s="3">
         <v>58400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>47900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>59000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>61500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>74800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>79900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>85000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>104700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>116900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>115100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>161600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>169000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2989,8 +3094,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2998,11 +3103,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>176000</v>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>176000</v>
@@ -3016,8 +3121,8 @@
       <c r="T47" s="3">
         <v>176000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>176000</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3025,50 +3130,53 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E48" s="3">
         <v>189300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>199300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>216600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>225300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>229200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>246600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>253400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>276300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>290000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>270200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>248300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>199300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3081,8 +3189,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3090,8 +3198,11 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3131,8 +3242,8 @@
       <c r="O49" s="3">
         <v>21200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>21200</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -3146,8 +3257,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3155,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,50 +3402,53 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E52" s="3">
         <v>5000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,8 +3461,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3350,8 +3470,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,73 +3538,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>270100</v>
+      </c>
+      <c r="E54" s="3">
         <v>273900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>273300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>301700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>313000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>330700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>353300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>365400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>406300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>430400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>407700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>432200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>390600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>176300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>176600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>176900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>177300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>177700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,115 +3660,119 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>23000</v>
+        <v>13300</v>
       </c>
       <c r="E57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F57" s="3">
         <v>16500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>31300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>31500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E58" s="3">
         <v>53500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>55300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>61300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>62900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>62000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>64900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>65900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>67100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>14000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3651,8 +3785,8 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3660,52 +3794,55 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>135300</v>
+        <v>121100</v>
       </c>
       <c r="E59" s="3">
+        <v>135800</v>
+      </c>
+      <c r="F59" s="3">
         <v>136100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>149000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>143000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>161000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>153600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>160000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>163300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>247500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>235100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>246200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>240100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>200</v>
@@ -3717,111 +3854,117 @@
         <v>200</v>
       </c>
       <c r="U59" s="3">
+        <v>200</v>
+      </c>
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>200100</v>
+      </c>
+      <c r="E60" s="3">
         <v>211900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>217500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>230600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>227600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>245200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>243700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>258900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>263900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>278100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>266100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>295500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>284800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>153600</v>
+      </c>
+      <c r="E61" s="3">
         <v>152600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>159000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>206200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>212400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>220700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>229100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>209900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>202600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3847,16 +3990,19 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>100</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3867,61 +4013,64 @@
         <v>3200</v>
       </c>
       <c r="F62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G62" s="3">
         <v>3000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>227200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>205300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>199000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>168200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22800</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,73 +4270,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>395300</v>
+      </c>
+      <c r="E66" s="3">
         <v>403700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>407900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>464200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>462900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>485400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>494900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>488300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>486300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>418600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>390300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>413800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>376600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>300</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4400,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,73 +4636,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-289600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-291200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-288900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-293200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-284500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-285800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-277000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-260300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-236900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-233900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-231300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-226400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-223400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-21500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,73 +4908,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-125200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-129900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-134600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-35200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-27500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-30200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-24100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-12000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>149600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>150800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>148900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>160600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>154500</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,50 +5213,51 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E83" s="3">
         <v>27700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5071,8 +5270,8 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5080,8 +5279,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E89" s="3">
         <v>6900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-16100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,55 +5715,56 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5551,8 +5772,8 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5560,8 +5781,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,50 +5917,53 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5746,8 +5976,8 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5755,8 +5985,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5809,8 +6043,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5819,11 +6053,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5845,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,50 +6283,53 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>5100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>25100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-12700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>66000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6096,8 +6342,8 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -6105,8 +6351,11 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6134,8 +6383,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6170,69 +6419,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E102" s="3">
         <v>10900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1200</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>ISPO</t>
   </si>
@@ -656,154 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E8" s="3">
         <v>65900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>63100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>69100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>80200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>70700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>82600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>84100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>91700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>86600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>93100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>83700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>82100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,8 +820,8 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -825,53 +829,56 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E9" s="3">
         <v>40300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>41200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>51200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>57700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>64700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>60100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>60700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>63000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>57400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>47300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -893,53 +900,56 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E10" s="3">
         <v>25500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>34800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,53 +1000,54 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2800</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,58 +1140,61 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-21100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>5900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1191,8 +1211,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1212,10 +1235,10 @@
         <v>1000</v>
       </c>
       <c r="I15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>1000</v>
@@ -1227,16 +1250,16 @@
         <v>1000</v>
       </c>
       <c r="N15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O15" s="3">
         <v>800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>700</v>
       </c>
       <c r="P15" s="3">
         <v>700</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>700</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1250,8 +1273,8 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1259,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,121 +1308,125 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E17" s="3">
         <v>64300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>67000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>82800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>82000</v>
       </c>
       <c r="H17" s="3">
         <v>82000</v>
       </c>
       <c r="I17" s="3">
+        <v>82000</v>
+      </c>
+      <c r="J17" s="3">
         <v>82100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>101800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>101000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>97400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>101000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>88500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>106100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
-      </c>
-      <c r="U17" s="3">
-        <v>100</v>
       </c>
       <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>100</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1409,17 +1439,20 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,41 +1477,42 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1488,8 +1522,8 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1503,62 +1537,65 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E21" s="3">
         <v>3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-13900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="I21" s="3">
         <v>3700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1617,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1595,25 +1635,25 @@
         <v>600</v>
       </c>
       <c r="G22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H22" s="3">
         <v>500</v>
       </c>
       <c r="I22" s="3">
+        <v>500</v>
+      </c>
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1648,102 +1688,108 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
       </c>
       <c r="G24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
       </c>
       <c r="L24" s="3">
         <v>200</v>
@@ -1760,8 +1806,8 @@
       <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>200</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1775,8 +1821,8 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1784,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-46700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,41 +2327,44 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2304,8 +2374,8 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2319,85 +2389,91 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,76 +2743,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>44400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>59900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>80300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>121300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,53 +2883,56 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2700</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2852,8 +2945,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2861,8 +2954,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2893,8 +2989,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2929,16 +3025,19 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1900</v>
       </c>
       <c r="F45" s="3">
         <v>1900</v>
@@ -2947,126 +3046,132 @@
         <v>1900</v>
       </c>
       <c r="H45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
-      </c>
-      <c r="T45" s="3">
-        <v>500</v>
       </c>
       <c r="U45" s="3">
         <v>500</v>
       </c>
       <c r="V45" s="3">
+        <v>500</v>
+      </c>
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E46" s="3">
         <v>55100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>58400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>47900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>59000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>61500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>74800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>79900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>85000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>104700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>116900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>115100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>161600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>169000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3097,8 +3202,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3106,11 +3211,11 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>176000</v>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>176000</v>
@@ -3124,8 +3229,8 @@
       <c r="U47" s="3">
         <v>176000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>176000</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3133,53 +3238,56 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>176400</v>
+      </c>
+      <c r="E48" s="3">
         <v>189200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>189300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>199300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>216600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>225300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>229200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>246600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>253400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>276300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>290000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>270200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>248300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>199300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3192,8 +3300,8 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3201,8 +3309,11 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3245,8 +3356,8 @@
       <c r="P49" s="3">
         <v>21200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>21200</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3260,8 +3371,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3269,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,53 +3522,56 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3464,8 +3584,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3473,8 +3593,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>252600</v>
+      </c>
+      <c r="E54" s="3">
         <v>270100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>273900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>273300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>301700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>313000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>330700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>353300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>365400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>406300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>430400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>407700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>432200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>390600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>176300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>176600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>176900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>177300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>177700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,121 +3791,125 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>32000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>30600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>31500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E58" s="3">
         <v>55300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>53500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>55300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>61300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>62900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>62000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>64900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>65900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>67100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>14000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,8 +3922,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3797,55 +3931,58 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E59" s="3">
         <v>121100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>135800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>136100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>149000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>143000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>161000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>153600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>160000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>163300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>247500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>235100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>246200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>240100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>200</v>
       </c>
       <c r="S59" s="3">
         <v>200</v>
@@ -3857,117 +3994,123 @@
         <v>200</v>
       </c>
       <c r="V59" s="3">
+        <v>200</v>
+      </c>
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>193300</v>
+      </c>
+      <c r="E60" s="3">
         <v>200100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>211900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>217500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>230600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>227600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>245200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>243700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>258900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>263900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>278100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>266100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>295500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>284800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E61" s="3">
         <v>153600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>152600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>159000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>206200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>212400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>220700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>229100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>209900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>202600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3993,16 +4136,19 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4016,61 +4162,64 @@
         <v>3200</v>
       </c>
       <c r="G62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H62" s="3">
         <v>3000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>227200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>205300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>199000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>168200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>27500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22800</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>382300</v>
+      </c>
+      <c r="E66" s="3">
         <v>395300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>403700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>407900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>464200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>462900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>485400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>494900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>488300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>486300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>418600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>390300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>413800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>376600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-294900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-289600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-291200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-288900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-293200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-284500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-285800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-277000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-260300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-236900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-233900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-231300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-226400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-223400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-26300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-25100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-21500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-129700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-125200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-129900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-134600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-35200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-27500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-30200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-24100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-12000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>149600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>150800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>148900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>160600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>154500</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,53 +5412,54 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16700</v>
+        <v>19300</v>
       </c>
       <c r="E83" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F83" s="3">
         <v>27700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5273,8 +5472,8 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5282,8 +5481,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-16100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,58 +5936,59 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5775,8 +5996,8 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5784,8 +6005,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,53 +6147,56 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5979,8 +6209,8 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5988,8 +6218,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6046,8 +6280,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6056,11 +6290,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6082,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,53 +6529,56 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>25100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-12700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>66000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6345,8 +6591,8 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -6354,8 +6600,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6386,8 +6635,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6422,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-39300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>52100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1200</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
